--- a/data/trans_orig/P3A_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153806</t>
+          <t>153385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200192</t>
+          <t>200279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78091</t>
+          <t>78775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116676</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246526</t>
+          <t>243829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307504</t>
+          <t>306270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>831531</t>
+          <t>831444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>877917</t>
+          <t>878338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1197422</t>
+          <t>1198167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1236007</t>
+          <t>1235323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2038317</t>
+          <t>2039551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2099295</t>
+          <t>2101992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>321059</t>
+          <t>322517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>390668</t>
+          <t>389001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163169</t>
+          <t>161398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213043</t>
+          <t>213236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>497770</t>
+          <t>499877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>585398</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1301863</t>
+          <t>1303530</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1371472</t>
+          <t>1370014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1372246</t>
+          <t>1372053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1422120</t>
+          <t>1423891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2692422</t>
+          <t>2690761</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2780050</t>
+          <t>2777943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129619</t>
+          <t>131377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174300</t>
+          <t>174934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102661</t>
+          <t>102900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141372</t>
+          <t>141467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244607</t>
+          <t>244058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>304441</t>
+          <t>302746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377108</t>
+          <t>376474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421789</t>
+          <t>420031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333886</t>
+          <t>333791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372597</t>
+          <t>372358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722225</t>
+          <t>723920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>782059</t>
+          <t>782608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>635310</t>
+          <t>640571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>729493</t>
+          <t>736856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>367940</t>
+          <t>371045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>443267</t>
+          <t>445792</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031181</t>
+          <t>1029471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1145058</t>
+          <t>1154499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2546168</t>
+          <t>2538805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2640351</t>
+          <t>2635090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2931378</t>
+          <t>2928853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3006705</t>
+          <t>3003600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5505249</t>
+          <t>5495808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5619126</t>
+          <t>5620836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>169830</t>
+          <t>170935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>223088</t>
+          <t>221524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84727</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125088</t>
+          <t>127352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271730</t>
+          <t>272939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337479</t>
+          <t>338057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>750495</t>
+          <t>752059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>803753</t>
+          <t>802648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1211709</t>
+          <t>1209445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1252070</t>
+          <t>1250110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1972902</t>
+          <t>1972324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2038651</t>
+          <t>2037442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>525848</t>
+          <t>527086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>608997</t>
+          <t>608693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260875</t>
+          <t>263069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>324745</t>
+          <t>326617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>803461</t>
+          <t>809606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>910473</t>
+          <t>912960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1354960</t>
+          <t>1355264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1438109</t>
+          <t>1436871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1432056</t>
+          <t>1430184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1495926</t>
+          <t>1493732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2810285</t>
+          <t>2807798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2917297</t>
+          <t>2911152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155464</t>
+          <t>155500</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200586</t>
+          <t>202386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109413</t>
+          <t>109272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151919</t>
+          <t>152540</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275888</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338981</t>
+          <t>338073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280595</t>
+          <t>278795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325717</t>
+          <t>325681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306712</t>
+          <t>306091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349218</t>
+          <t>349359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600832</t>
+          <t>601740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663925</t>
+          <t>661098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>890749</t>
+          <t>886466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>997745</t>
+          <t>989381</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>481568</t>
+          <t>483373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>575339</t>
+          <t>573080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1404019</t>
+          <t>1401412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1550651</t>
+          <t>1543626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2420977</t>
+          <t>2429341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2527973</t>
+          <t>2532256</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2976890</t>
+          <t>2979149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3070661</t>
+          <t>3068856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5420300</t>
+          <t>5427325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5566932</t>
+          <t>5569539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>143660</t>
+          <t>140765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187831</t>
+          <t>186879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66136</t>
+          <t>65993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102339</t>
+          <t>100266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218429</t>
+          <t>216665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277293</t>
+          <t>276042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>563826</t>
+          <t>564778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>607997</t>
+          <t>610892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>890264</t>
+          <t>892337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>926467</t>
+          <t>926610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1466967</t>
+          <t>1468218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1525831</t>
+          <t>1527595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>656738</t>
+          <t>658313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>743902</t>
+          <t>744941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>363678</t>
+          <t>367037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>436923</t>
+          <t>438971</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1038866</t>
+          <t>1042082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1156850</t>
+          <t>1160195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1327104</t>
+          <t>1326065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1414268</t>
+          <t>1412693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1549402</t>
+          <t>1547354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1622647</t>
+          <t>1619288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2900481</t>
+          <t>2897136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3018465</t>
+          <t>3015249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208416</t>
+          <t>208645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254194</t>
+          <t>256369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155038</t>
+          <t>154831</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199602</t>
+          <t>200810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376929</t>
+          <t>375780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>439047</t>
+          <t>443145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291720</t>
+          <t>289545</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337498</t>
+          <t>337269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>348609</t>
+          <t>347401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393173</t>
+          <t>393380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655078</t>
+          <t>650980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>717196</t>
+          <t>718345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,65%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1039843</t>
+          <t>1036156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1150247</t>
+          <t>1149815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>608734</t>
+          <t>614861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>701762</t>
+          <t>704700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1677993</t>
+          <t>1673212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1817881</t>
+          <t>1819054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2218330</t>
+          <t>2218762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2328734</t>
+          <t>2332421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2825377</t>
+          <t>2822439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2918405</t>
+          <t>2912278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5077835</t>
+          <t>5076662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5217723</t>
+          <t>5222504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72727</t>
+          <t>73521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103911</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56728</t>
+          <t>56160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82447</t>
+          <t>81128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>136109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178056</t>
+          <t>175825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411027</t>
+          <t>409736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>442211</t>
+          <t>441417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>673061</t>
+          <t>674380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>698780</t>
+          <t>699348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1092390</t>
+          <t>1094621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1134135</t>
+          <t>1134337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>424486</t>
+          <t>394805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>687327</t>
+          <t>685188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327510</t>
+          <t>346621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>532977</t>
+          <t>534146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839336</t>
+          <t>845573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1187946</t>
+          <t>1191006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1601901</t>
+          <t>1604040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1864742</t>
+          <t>1894423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1703587</t>
+          <t>1702418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1909054</t>
+          <t>1889943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3337846</t>
+          <t>3334786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3686456</t>
+          <t>3680219</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>220435</t>
+          <t>221724</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271649</t>
+          <t>270865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186085</t>
+          <t>185762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228439</t>
+          <t>226033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>418020</t>
+          <t>418228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>484115</t>
+          <t>484398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>374974</t>
+          <t>375758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426188</t>
+          <t>424899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>432024</t>
+          <t>434430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474378</t>
+          <t>474701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822971</t>
+          <t>822688</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>889066</t>
+          <t>888858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>720248</t>
+          <t>714371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1024288</t>
+          <t>1021495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>588826</t>
+          <t>590124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>800478</t>
+          <t>800445</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1449910</t>
+          <t>1463184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1785932</t>
+          <t>1778026</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2426502</t>
+          <t>2429295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2730542</t>
+          <t>2736419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2852057</t>
+          <t>2852090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3063709</t>
+          <t>3062411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5317392</t>
+          <t>5325298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5653414</t>
+          <t>5640140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R1-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153385</t>
+          <t>154138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200279</t>
+          <t>201025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78775</t>
+          <t>79837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115931</t>
+          <t>116595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243829</t>
+          <t>242103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306270</t>
+          <t>303081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>831444</t>
+          <t>830698</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>878338</t>
+          <t>877585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1198167</t>
+          <t>1197503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1235323</t>
+          <t>1234261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2039551</t>
+          <t>2042740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2101992</t>
+          <t>2103718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>322517</t>
+          <t>326463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>389001</t>
+          <t>396012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161398</t>
+          <t>162279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213236</t>
+          <t>213094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>499877</t>
+          <t>500576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587059</t>
+          <t>586838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1303530</t>
+          <t>1296519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1370014</t>
+          <t>1366068</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1372053</t>
+          <t>1372195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1423891</t>
+          <t>1423010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2690761</t>
+          <t>2690982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2777943</t>
+          <t>2777244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131377</t>
+          <t>129476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174934</t>
+          <t>173540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102900</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141467</t>
+          <t>140105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244058</t>
+          <t>242767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>302746</t>
+          <t>305373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376474</t>
+          <t>377868</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>420031</t>
+          <t>421932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333791</t>
+          <t>335153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372358</t>
+          <t>373788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>723920</t>
+          <t>721293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>782608</t>
+          <t>783899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>640571</t>
+          <t>639436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>736856</t>
+          <t>734655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>371045</t>
+          <t>367576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>445792</t>
+          <t>444153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1029471</t>
+          <t>1027807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1154499</t>
+          <t>1148678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2538805</t>
+          <t>2541006</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2635090</t>
+          <t>2636225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2928853</t>
+          <t>2930492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3003600</t>
+          <t>3007069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5495808</t>
+          <t>5501629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5620836</t>
+          <t>5622500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170935</t>
+          <t>170131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>221524</t>
+          <t>222375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86687</t>
+          <t>87205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127352</t>
+          <t>126504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272939</t>
+          <t>272541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>338057</t>
+          <t>341164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>752059</t>
+          <t>751208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>802648</t>
+          <t>803452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1209445</t>
+          <t>1210293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1250110</t>
+          <t>1249592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1972324</t>
+          <t>1969217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2037442</t>
+          <t>2037840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>527086</t>
+          <t>526769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>608693</t>
+          <t>611714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>265479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>326617</t>
+          <t>327052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>809606</t>
+          <t>807957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>912960</t>
+          <t>910111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1355264</t>
+          <t>1352243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1436871</t>
+          <t>1437188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1430184</t>
+          <t>1429749</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1493732</t>
+          <t>1491322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2807798</t>
+          <t>2810647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2911152</t>
+          <t>2912801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155500</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202386</t>
+          <t>199416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109272</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152540</t>
+          <t>150582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>273789</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338073</t>
+          <t>337358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278795</t>
+          <t>281765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325681</t>
+          <t>326132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306091</t>
+          <t>308049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>349359</t>
+          <t>348885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>601740</t>
+          <t>602455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661098</t>
+          <t>666024</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>886466</t>
+          <t>892119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>989381</t>
+          <t>998874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>483373</t>
+          <t>488860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>573080</t>
+          <t>573361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1401412</t>
+          <t>1397417</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1543626</t>
+          <t>1540491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2429341</t>
+          <t>2419848</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2532256</t>
+          <t>2526603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2979149</t>
+          <t>2978868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3068856</t>
+          <t>3063369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5427325</t>
+          <t>5430460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5569539</t>
+          <t>5573534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140765</t>
+          <t>141553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>186879</t>
+          <t>184213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65993</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100266</t>
+          <t>100379</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216665</t>
+          <t>217213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276042</t>
+          <t>273972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564778</t>
+          <t>567444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>610892</t>
+          <t>610104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>892337</t>
+          <t>892224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>926610</t>
+          <t>927504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1468218</t>
+          <t>1470288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1527595</t>
+          <t>1527047</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>658313</t>
+          <t>655906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>744941</t>
+          <t>743279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>367037</t>
+          <t>364511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>438971</t>
+          <t>435954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1042082</t>
+          <t>1039742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1160195</t>
+          <t>1160315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1326065</t>
+          <t>1327727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1412693</t>
+          <t>1415100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1547354</t>
+          <t>1550371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1619288</t>
+          <t>1621814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2897136</t>
+          <t>2897016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3015249</t>
+          <t>3017589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208645</t>
+          <t>206521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256369</t>
+          <t>253593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154831</t>
+          <t>155764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200810</t>
+          <t>199239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375780</t>
+          <t>373722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443145</t>
+          <t>439918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289545</t>
+          <t>292321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337269</t>
+          <t>339393</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>348972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>392447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650980</t>
+          <t>654207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718345</t>
+          <t>720403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,84%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1036156</t>
+          <t>1035242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1149815</t>
+          <t>1144253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>614861</t>
+          <t>607513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>704700</t>
+          <t>700908</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1673212</t>
+          <t>1670292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1819054</t>
+          <t>1821511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2218762</t>
+          <t>2224324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2332421</t>
+          <t>2333335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2822439</t>
+          <t>2826231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2912278</t>
+          <t>2919626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5076662</t>
+          <t>5074205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5222504</t>
+          <t>5225424</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>97903</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73521</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>117737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>72238</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>60587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81128</t>
+          <t>86919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>155506</t>
+          <t>170141</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136109</t>
+          <t>149133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175825</t>
+          <t>192435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>426696</t>
+          <t>480626</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409736</t>
+          <t>460792</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>441417</t>
+          <t>496071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>688244</t>
+          <t>749800</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>674380</t>
+          <t>735119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>699348</t>
+          <t>761451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1114940</t>
+          <t>1230426</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1094621</t>
+          <t>1208132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1134337</t>
+          <t>1251434</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>651692</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>394805</t>
+          <t>605770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>685188</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>462534</t>
+          <t>503911</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>346621</t>
+          <t>468217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>534146</t>
+          <t>537633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1058896</t>
+          <t>1155603</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>845573</t>
+          <t>1096040</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1191006</t>
+          <t>1212198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1692866</t>
+          <t>1577781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1604040</t>
+          <t>1527924</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1894423</t>
+          <t>1623703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1774030</t>
+          <t>1666236</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1702418</t>
+          <t>1632514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1889943</t>
+          <t>1701930</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3466896</t>
+          <t>3244017</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3334786</t>
+          <t>3187422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3680219</t>
+          <t>3303580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>245513</t>
+          <t>272541</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221724</t>
+          <t>246774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270865</t>
+          <t>302014</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>204985</t>
+          <t>220236</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>185762</t>
+          <t>198586</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>226033</t>
+          <t>243695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>450498</t>
+          <t>492777</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>418228</t>
+          <t>462304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>484398</t>
+          <t>532519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>401110</t>
+          <t>439046</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>375758</t>
+          <t>409573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424899</t>
+          <t>464813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455478</t>
+          <t>514641</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434430</t>
+          <t>491182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>474701</t>
+          <t>536291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>856588</t>
+          <t>953687</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822688</t>
+          <t>913945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888858</t>
+          <t>984160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>930117</t>
+          <t>1022136</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>714371</t>
+          <t>962868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1021495</t>
+          <t>1080225</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>734783</t>
+          <t>796384</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>590124</t>
+          <t>757921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>800445</t>
+          <t>838919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1664900</t>
+          <t>1818520</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1463184</t>
+          <t>1746876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1778026</t>
+          <t>1892981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2520673</t>
+          <t>2497454</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2429295</t>
+          <t>2439365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2736419</t>
+          <t>2556722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2917752</t>
+          <t>2930678</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2852090</t>
+          <t>2888143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3062411</t>
+          <t>2969141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5438424</t>
+          <t>5428132</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5325298</t>
+          <t>5353671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5640140</t>
+          <t>5499776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
